--- a/TPE_25P822_N3.xlsx
+++ b/TPE_25P822_N3.xlsx
@@ -20,12 +20,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="87">
-  <si>
-    <t xml:space="preserve">RÉFÉRENTIEL COSO 2013 — Les 5 Composantes &amp; les 17 Principes  ·  Audit des Systèmes d'Information</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Committee of Sponsoring Organizations of the Treadway Commission  ·  COSO 2013</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="69">
+  <si>
+    <t xml:space="preserve">RÉFÉRENTIEL COSO 2013 Les 5 Composantes &amp; les 17 Principes  ·  Audit des Systèmes d'Information</t>
   </si>
   <si>
     <t xml:space="preserve">N°</t>
@@ -46,9 +43,6 @@
     <t xml:space="preserve">Description — Application en Audit SI</t>
   </si>
   <si>
-    <t xml:space="preserve">Standards SI</t>
-  </si>
-  <si>
     <t xml:space="preserve">C1</t>
   </si>
   <si>
@@ -64,9 +58,6 @@
     <t xml:space="preserve">Charte éthique IT, politique d'usage acceptable des ressources informatiques, mécanismes de signalement des anomalies (whistleblowing) dans le SI.</t>
   </si>
   <si>
-    <t xml:space="preserve">ISO 27001 A.5</t>
-  </si>
-  <si>
     <t xml:space="preserve">P2</t>
   </si>
   <si>
@@ -76,9 +67,6 @@
     <t xml:space="preserve">Comité d'audit SI, validation de la stratégie informatique, supervision des risques cyber, revue des incidents de sécurité majeurs.</t>
   </si>
   <si>
-    <t xml:space="preserve">COBIT EDM01</t>
-  </si>
-  <si>
     <t xml:space="preserve">P3</t>
   </si>
   <si>
@@ -88,9 +76,6 @@
     <t xml:space="preserve">Organigramme DSI, rôles RSSI/DPO/DSI, matrice RACI, séparation des fonctions Dev/Exploitation/Sécurité.</t>
   </si>
   <si>
-    <t xml:space="preserve">ISO 27001 A.6</t>
-  </si>
-  <si>
     <t xml:space="preserve">P4</t>
   </si>
   <si>
@@ -100,9 +85,6 @@
     <t xml:space="preserve">Plans de formation cybersécurité, certifications (CISA, CISSP, ISO 27001 LA), matrices de compétences, GPEC-IT.</t>
   </si>
   <si>
-    <t xml:space="preserve">ISO 27001 A.7</t>
-  </si>
-  <si>
     <t xml:space="preserve">P5</t>
   </si>
   <si>
@@ -112,9 +94,6 @@
     <t xml:space="preserve">Objectifs de sécurité SI dans les évaluations de performance, mesures correctives documentées et tracées.</t>
   </si>
   <si>
-    <t xml:space="preserve">COBIT EDM02</t>
-  </si>
-  <si>
     <t xml:space="preserve">C2</t>
   </si>
   <si>
@@ -139,9 +118,6 @@
     <t xml:space="preserve">Cartographie des risques SI, analyses EBIOS RM / ISO 27005, inventaire des actifs informationnels, scénarios de menaces cyber.</t>
   </si>
   <si>
-    <t xml:space="preserve">ISO 27005 / EBIOS</t>
-  </si>
-  <si>
     <t xml:space="preserve">P8</t>
   </si>
   <si>
@@ -151,9 +127,6 @@
     <t xml:space="preserve">Fraude informatique (ERP, BEC, usurpation d'identité numérique), contrôles applicatifs anti-fraude, pistes d'audit.</t>
   </si>
   <si>
-    <t xml:space="preserve">COBIT APO12</t>
-  </si>
-  <si>
     <t xml:space="preserve">P9</t>
   </si>
   <si>
@@ -163,9 +136,6 @@
     <t xml:space="preserve">ITIL Change Management, migrations, déploiements cloud, nouvelles réglementations (RGPD, DORA, NIS2).</t>
   </si>
   <si>
-    <t xml:space="preserve">ITIL 4 / DORA</t>
-  </si>
-  <si>
     <t xml:space="preserve">C3</t>
   </si>
   <si>
@@ -181,9 +151,6 @@
     <t xml:space="preserve">ITGC : contrôles d'accès logiques (IAM/MFA/RBAC), sauvegardes, gestion des patches, séparation Dev/Test/Prod, journalisation.</t>
   </si>
   <si>
-    <t xml:space="preserve">CIS Benchmarks</t>
-  </si>
-  <si>
     <t xml:space="preserve">P11</t>
   </si>
   <si>
@@ -193,9 +160,6 @@
     <t xml:space="preserve">Hardening des OS, configuration firewall/IDS/IPS/VPN, gestion des CVE, chiffrement, gestion des clés cryptographiques.</t>
   </si>
   <si>
-    <t xml:space="preserve">ISO 27001 A.8 / OWASP</t>
-  </si>
-  <si>
     <t xml:space="preserve">P12</t>
   </si>
   <si>
@@ -205,9 +169,6 @@
     <t xml:space="preserve">PSSI, procédures de gestion des incidents, charte informatique, développement sécurisé (OWASP, DevSecOps), CAB.</t>
   </si>
   <si>
-    <t xml:space="preserve">ITIL 4 / ISO 27001</t>
-  </si>
-  <si>
     <t xml:space="preserve">C4</t>
   </si>
   <si>
@@ -223,9 +184,6 @@
     <t xml:space="preserve">Intégrité des données applicatives, fiabilité des logs/traces d'audit, exactitude des référentiels (IAM, CMDB), conformité RGPD.</t>
   </si>
   <si>
-    <t xml:space="preserve">RGPD / ISO 27701</t>
-  </si>
-  <si>
     <t xml:space="preserve">P14</t>
   </si>
   <si>
@@ -235,9 +193,6 @@
     <t xml:space="preserve">Reporting RSSI→COMEX, diffusion des politiques de sécurité, communication des incidents, tableaux de bord SI (COSEC).</t>
   </si>
   <si>
-    <t xml:space="preserve">COBIT MEA01</t>
-  </si>
-  <si>
     <t xml:space="preserve">P15</t>
   </si>
   <si>
@@ -247,9 +202,6 @@
     <t xml:space="preserve">Notification CNIL (72h — RGPD Art.33), communication ANSSI/CERT-FR, information clients, relations auditeurs externes.</t>
   </si>
   <si>
-    <t xml:space="preserve">RGPD Art.33 / NIS2</t>
-  </si>
-  <si>
     <t xml:space="preserve">C5</t>
   </si>
   <si>
@@ -265,9 +217,6 @@
     <t xml:space="preserve">Supervision SIEM, SOC 24/7, monitoring des accès, audits ISO 27001, pentests, revues de code, exercices Red/Blue Team, DORA.</t>
   </si>
   <si>
-    <t xml:space="preserve">NIST CSF / ISO 27035</t>
-  </si>
-  <si>
     <t xml:space="preserve">P17</t>
   </si>
   <si>
@@ -275,9 +224,6 @@
   </si>
   <si>
     <t xml:space="preserve">Registre des non-conformités, communication formelle des failles à la direction, plans d'action (CAP), suivi et clôture des actions correctives.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ISO 27001 A.9</t>
   </si>
   <si>
     <r>
@@ -326,7 +272,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="18">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -358,14 +304,6 @@
       <charset val="1"/>
     </font>
     <font>
-      <i val="true"/>
-      <sz val="9"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
       <b val="true"/>
       <sz val="9"/>
       <color rgb="FFFFFFFF"/>
@@ -400,14 +338,6 @@
     <font>
       <sz val="10"/>
       <color rgb="FF333333"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <i val="true"/>
-      <sz val="10"/>
-      <color rgb="FF444444"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -491,12 +421,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF1F3864"/>
         <bgColor rgb="FF333333"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2E75B6"/>
-        <bgColor rgb="FF0066CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -519,8 +443,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF2E75B6"/>
+        <bgColor rgb="FF0066CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF375623"/>
-        <bgColor rgb="FF444444"/>
+        <bgColor rgb="FF555555"/>
       </patternFill>
     </fill>
     <fill>
@@ -560,7 +490,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="18">
+  <borders count="13">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -614,21 +544,6 @@
       <diagonal/>
     </border>
     <border diagonalUp="false" diagonalDown="false">
-      <left style="thin">
-        <color rgb="FFC0C0C0"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF1F3864"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFC0C0C0"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFC0C0C0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
       <left style="medium">
         <color rgb="FF2E75B6"/>
       </left>
@@ -652,21 +567,6 @@
       </right>
       <top style="medium">
         <color rgb="FF2E75B6"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFC0C0C0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin">
-        <color rgb="FFC0C0C0"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF2E75B6"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFC0C0C0"/>
       </top>
       <bottom style="thin">
         <color rgb="FFC0C0C0"/>
@@ -704,21 +604,6 @@
       <diagonal/>
     </border>
     <border diagonalUp="false" diagonalDown="false">
-      <left style="thin">
-        <color rgb="FFC0C0C0"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF375623"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFC0C0C0"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFC0C0C0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
       <left style="medium">
         <color rgb="FF7030A0"/>
       </left>
@@ -742,21 +627,6 @@
       </right>
       <top style="medium">
         <color rgb="FF7030A0"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFC0C0C0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin">
-        <color rgb="FFC0C0C0"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF7030A0"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFC0C0C0"/>
       </top>
       <bottom style="thin">
         <color rgb="FFC0C0C0"/>
@@ -787,21 +657,6 @@
       </right>
       <top style="medium">
         <color rgb="FFC55A11"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFC0C0C0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin">
-        <color rgb="FFC0C0C0"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFC55A11"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFC0C0C0"/>
       </top>
       <bottom style="thin">
         <color rgb="FFC0C0C0"/>
@@ -847,7 +702,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="41">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -856,15 +711,11 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -872,167 +723,147 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="4" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="6" fillId="6" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="6" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="6" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="7" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="7" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="7" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="9" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="9" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="9" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="4" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="7" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="7" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="7" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="8" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="9" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="9" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="9" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="10" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="11" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="11" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="11" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="12" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="12" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="12" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="12" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="13" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="11" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="11" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="11" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="12" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="12" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="12" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="13" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1097,8 +928,8 @@
       <rgbColor rgb="FF969696"/>
       <rgbColor rgb="FF1F3864"/>
       <rgbColor rgb="FF3FAF46"/>
+      <rgbColor rgb="FF003300"/>
       <rgbColor rgb="FF375623"/>
-      <rgbColor rgb="FF444444"/>
       <rgbColor rgb="FF993300"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
@@ -1113,8 +944,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:F1048576"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="8"/>
@@ -1122,7 +953,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="7"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="30"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1024" min="1024" style="0" width="9.14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1134,429 +965,358 @@
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-    </row>
-    <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-    </row>
-    <row r="3" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="E2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="F2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="3" t="s">
+    </row>
+    <row r="3" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="C3" s="5" t="s">
         <v>8</v>
       </c>
+      <c r="D3" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="8" t="s">
+      <c r="A4" s="3"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="E4" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="G4" s="10" t="s">
+      <c r="F4" s="10" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4"/>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="7" t="s">
+      <c r="A5" s="3"/>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="11" t="s">
+      <c r="E5" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="F5" s="12" t="s">
+      <c r="F5" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="G5" s="10" t="s">
+    </row>
+    <row r="6" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="6" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4"/>
-      <c r="B6" s="5"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="7" t="s">
+      <c r="E6" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="F6" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F6" s="9" t="s">
+    </row>
+    <row r="7" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="G6" s="10" t="s">
+      <c r="E7" s="7" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4"/>
-      <c r="B7" s="5"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="7" t="s">
+      <c r="F7" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="E7" s="11" t="s">
+    </row>
+    <row r="8" customFormat="false" ht="4.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="11"/>
+      <c r="B8" s="11"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
+    </row>
+    <row r="9" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="F7" s="12" t="s">
+      <c r="C9" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="G7" s="10" t="s">
+      <c r="D9" s="16" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="8" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4"/>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="7" t="s">
+      <c r="E9" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="F9" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="F8" s="9" t="s">
+    </row>
+    <row r="10" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="13"/>
+      <c r="B10" s="14"/>
+      <c r="C10" s="14"/>
+      <c r="D10" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="G8" s="10" t="s">
+      <c r="E10" s="18" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="9" customFormat="false" ht="4.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="13"/>
-      <c r="B9" s="13"/>
-      <c r="C9" s="13"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-    </row>
-    <row r="10" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="B10" s="16" t="s">
+      <c r="F10" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="C10" s="17" t="s">
+    </row>
+    <row r="11" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="13"/>
+      <c r="B11" s="14"/>
+      <c r="C11" s="14"/>
+      <c r="D11" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="D10" s="18" t="s">
+      <c r="E11" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="E10" s="19" t="s">
+      <c r="F11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="F10" s="9" t="s">
+    </row>
+    <row r="12" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="13"/>
+      <c r="B12" s="14"/>
+      <c r="C12" s="14"/>
+      <c r="D12" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="G10" s="20" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="15"/>
-      <c r="B11" s="16"/>
-      <c r="C11" s="16"/>
-      <c r="D11" s="18" t="s">
+      <c r="E12" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="E11" s="21" t="s">
+      <c r="F12" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="F11" s="12" t="s">
+    </row>
+    <row r="13" customFormat="false" ht="4.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="11"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="12"/>
+    </row>
+    <row r="14" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="B14" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="G11" s="20" t="s">
+      <c r="C14" s="21" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="12" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="15"/>
-      <c r="B12" s="16"/>
-      <c r="C12" s="16"/>
-      <c r="D12" s="18" t="s">
+      <c r="D14" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="E12" s="19" t="s">
+      <c r="E14" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="F12" s="9" t="s">
+      <c r="F14" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="G12" s="20" t="s">
+    </row>
+    <row r="15" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="19"/>
+      <c r="B15" s="20"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="22" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="13" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="15"/>
-      <c r="B13" s="16"/>
-      <c r="C13" s="16"/>
-      <c r="D13" s="18" t="s">
+      <c r="E15" s="25" t="s">
         <v>44</v>
       </c>
-      <c r="E13" s="21" t="s">
+      <c r="F15" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="F13" s="12" t="s">
+    </row>
+    <row r="16" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="19"/>
+      <c r="B16" s="20"/>
+      <c r="C16" s="20"/>
+      <c r="D16" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="G13" s="20" t="s">
+      <c r="E16" s="23" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="14" customFormat="false" ht="4.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="13"/>
-      <c r="B14" s="13"/>
-      <c r="C14" s="13"/>
-      <c r="D14" s="13"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-    </row>
-    <row r="15" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="22" t="n">
-        <v>3</v>
-      </c>
-      <c r="B15" s="23" t="s">
+      <c r="F16" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="C15" s="24" t="s">
+    </row>
+    <row r="17" customFormat="false" ht="4.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="11"/>
+      <c r="B17" s="11"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="12"/>
+      <c r="F17" s="12"/>
+    </row>
+    <row r="18" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="B18" s="27" t="s">
         <v>49</v>
       </c>
-      <c r="D15" s="25" t="s">
+      <c r="C18" s="28" t="s">
         <v>50</v>
       </c>
-      <c r="E15" s="26" t="s">
+      <c r="D18" s="29" t="s">
         <v>51</v>
       </c>
-      <c r="F15" s="27" t="s">
+      <c r="E18" s="30" t="s">
         <v>52</v>
       </c>
-      <c r="G15" s="28" t="s">
+      <c r="F18" s="31" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="22"/>
-      <c r="B16" s="23"/>
-      <c r="C16" s="23"/>
-      <c r="D16" s="25" t="s">
+    <row r="19" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="26"/>
+      <c r="B19" s="27"/>
+      <c r="C19" s="27"/>
+      <c r="D19" s="29" t="s">
         <v>54</v>
       </c>
-      <c r="E16" s="29" t="s">
+      <c r="E19" s="32" t="s">
         <v>55</v>
       </c>
-      <c r="F16" s="12" t="s">
+      <c r="F19" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="G16" s="28" t="s">
+    </row>
+    <row r="20" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="26"/>
+      <c r="B20" s="27"/>
+      <c r="C20" s="27"/>
+      <c r="D20" s="29" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="17" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="22"/>
-      <c r="B17" s="23"/>
-      <c r="C17" s="23"/>
-      <c r="D17" s="25" t="s">
+      <c r="E20" s="30" t="s">
         <v>58</v>
       </c>
-      <c r="E17" s="26" t="s">
+      <c r="F20" s="31" t="s">
         <v>59</v>
       </c>
-      <c r="F17" s="27" t="s">
+    </row>
+    <row r="21" customFormat="false" ht="4.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="11"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="12"/>
+    </row>
+    <row r="22" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="33" t="n">
+        <v>5</v>
+      </c>
+      <c r="B22" s="34" t="s">
         <v>60</v>
       </c>
-      <c r="G17" s="28" t="s">
+      <c r="C22" s="35" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="18" customFormat="false" ht="4.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="13"/>
-      <c r="B18" s="13"/>
-      <c r="C18" s="13"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-    </row>
-    <row r="19" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="30" t="n">
-        <v>4</v>
-      </c>
-      <c r="B19" s="31" t="s">
+      <c r="D22" s="36" t="s">
         <v>62</v>
       </c>
-      <c r="C19" s="32" t="s">
+      <c r="E22" s="37" t="s">
         <v>63</v>
       </c>
-      <c r="D19" s="33" t="s">
+      <c r="F22" s="38" t="s">
         <v>64</v>
       </c>
-      <c r="E19" s="34" t="s">
+    </row>
+    <row r="23" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="33"/>
+      <c r="B23" s="34"/>
+      <c r="C23" s="34"/>
+      <c r="D23" s="36" t="s">
         <v>65</v>
       </c>
-      <c r="F19" s="35" t="s">
+      <c r="E23" s="39" t="s">
         <v>66</v>
       </c>
-      <c r="G19" s="36" t="s">
+      <c r="F23" s="10" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="30"/>
-      <c r="B20" s="31"/>
-      <c r="C20" s="31"/>
-      <c r="D20" s="33" t="s">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="25" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="40" t="s">
         <v>68</v>
       </c>
-      <c r="E20" s="37" t="s">
-        <v>69</v>
-      </c>
-      <c r="F20" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="G20" s="36" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="30"/>
-      <c r="B21" s="31"/>
-      <c r="C21" s="31"/>
-      <c r="D21" s="33" t="s">
-        <v>72</v>
-      </c>
-      <c r="E21" s="34" t="s">
-        <v>73</v>
-      </c>
-      <c r="F21" s="35" t="s">
-        <v>74</v>
-      </c>
-      <c r="G21" s="36" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="4.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="13"/>
-      <c r="B22" s="13"/>
-      <c r="C22" s="13"/>
-      <c r="D22" s="13"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-    </row>
-    <row r="23" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="38" t="n">
-        <v>5</v>
-      </c>
-      <c r="B23" s="39" t="s">
-        <v>76</v>
-      </c>
-      <c r="C23" s="40" t="s">
-        <v>77</v>
-      </c>
-      <c r="D23" s="41" t="s">
-        <v>78</v>
-      </c>
-      <c r="E23" s="42" t="s">
-        <v>79</v>
-      </c>
-      <c r="F23" s="43" t="s">
-        <v>80</v>
-      </c>
-      <c r="G23" s="44" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="38"/>
-      <c r="B24" s="39"/>
-      <c r="C24" s="39"/>
-      <c r="D24" s="41" t="s">
-        <v>82</v>
-      </c>
-      <c r="E24" s="45" t="s">
-        <v>83</v>
-      </c>
-      <c r="F24" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="G24" s="44" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="46" t="s">
-        <v>86</v>
-      </c>
-      <c r="B26" s="46"/>
-      <c r="C26" s="46"/>
-      <c r="D26" s="46"/>
-      <c r="E26" s="46"/>
-      <c r="F26" s="46"/>
-      <c r="G26" s="46"/>
-    </row>
-    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+      <c r="B25" s="40"/>
+      <c r="C25" s="40"/>
+      <c r="D25" s="40"/>
+      <c r="E25" s="40"/>
+      <c r="F25" s="40"/>
+    </row>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <mergeCells count="18">
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A4:A8"/>
-    <mergeCell ref="B4:B8"/>
-    <mergeCell ref="C4:C8"/>
-    <mergeCell ref="A10:A13"/>
-    <mergeCell ref="B10:B13"/>
-    <mergeCell ref="C10:C13"/>
-    <mergeCell ref="A15:A17"/>
-    <mergeCell ref="B15:B17"/>
-    <mergeCell ref="C15:C17"/>
-    <mergeCell ref="A19:A21"/>
-    <mergeCell ref="B19:B21"/>
-    <mergeCell ref="C19:C21"/>
-    <mergeCell ref="A23:A24"/>
-    <mergeCell ref="B23:B24"/>
-    <mergeCell ref="C23:C24"/>
-    <mergeCell ref="A26:G26"/>
+  <mergeCells count="17">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A3:A7"/>
+    <mergeCell ref="B3:B7"/>
+    <mergeCell ref="C3:C7"/>
+    <mergeCell ref="A9:A12"/>
+    <mergeCell ref="B9:B12"/>
+    <mergeCell ref="C9:C12"/>
+    <mergeCell ref="A14:A16"/>
+    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="C14:C16"/>
+    <mergeCell ref="A18:A20"/>
+    <mergeCell ref="B18:B20"/>
+    <mergeCell ref="C18:C20"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="A25:F25"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
